--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X9.cis.beta.carotene/Resultats_X9.cis.beta.carotene_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X9.cis.beta.carotene/Resultats_X9.cis.beta.carotene_moy_ADJR2.xlsx
@@ -1,208 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\X9.cis.beta.carotene\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV0_ADJR2</t>
-  </si>
-  <si>
-    <t>LV1_ADJR2</t>
-  </si>
-  <si>
-    <t>LV2_ADJR2</t>
-  </si>
-  <si>
-    <t>LV3_ADJR2</t>
-  </si>
-  <si>
-    <t>LV4_ADJR2</t>
-  </si>
-  <si>
-    <t>LV5_ADJR2</t>
-  </si>
-  <si>
-    <t>LV6_ADJR2</t>
-  </si>
-  <si>
-    <t>LV7_ADJR2</t>
-  </si>
-  <si>
-    <t>LV8_ADJR2</t>
-  </si>
-  <si>
-    <t>LV9_ADJR2</t>
-  </si>
-  <si>
-    <t>LV10_ADJR2</t>
-  </si>
-  <si>
-    <t>LV11_ADJR2</t>
-  </si>
-  <si>
-    <t>LV12_ADJR2</t>
-  </si>
-  <si>
-    <t>LV13_ADJR2</t>
-  </si>
-  <si>
-    <t>LV14_ADJR2</t>
-  </si>
-  <si>
-    <t>LV15_ADJR2</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -235,95 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -365,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -397,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -432,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -608,2308 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_ADJR2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_ADJR2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_ADJR2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_ADJR2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_ADJR2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_ADJR2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_ADJR2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_ADJR2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_ADJR2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_ADJR2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_ADJR2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_ADJR2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_ADJR2</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_ADJR2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_ADJR2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_ADJR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>0.33590940001742381</v>
+        <v>0.3359094003683077</v>
       </c>
       <c r="D2">
-        <v>0.45145419926068397</v>
+        <v>0.4514541995940585</v>
       </c>
       <c r="E2">
-        <v>0.48819127067429019</v>
+        <v>0.4881912712135</v>
       </c>
       <c r="F2">
-        <v>0.51820661692297743</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.53991659766715305</v>
+        <v>0.5182066173252611</v>
+      </c>
+      <c r="G2">
+        <v>0.5399165981726622</v>
       </c>
       <c r="H2">
-        <v>0.56574182162917341</v>
+        <v>0.5657418215311074</v>
       </c>
       <c r="I2">
-        <v>0.58621886602662387</v>
+        <v>0.5862188650751718</v>
       </c>
       <c r="J2">
-        <v>0.58684620018236255</v>
+        <v>0.586846199325236</v>
       </c>
       <c r="K2">
-        <v>0.60655795435717252</v>
+        <v>0.6065579534969281</v>
       </c>
       <c r="L2">
-        <v>0.6008205972505164</v>
+        <v>0.6008205969766268</v>
       </c>
       <c r="M2">
-        <v>0.58814214989560332</v>
+        <v>0.5881421499576279</v>
       </c>
       <c r="N2">
-        <v>0.55409388319704356</v>
+        <v>0.5540938839112433</v>
       </c>
       <c r="O2">
-        <v>0.4824040884186141</v>
+        <v>0.4824040879163796</v>
       </c>
       <c r="P2">
-        <v>0.39053816849609008</v>
+        <v>0.3905381639243802</v>
       </c>
       <c r="Q2">
-        <v>0.36315900958741248</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
+        <v>0.3631590029371821</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.37417877872341959</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C3">
+        <v>0.3741787726582632</v>
       </c>
       <c r="D3">
-        <v>0.46512098529108231</v>
+        <v>0.4651209866793252</v>
       </c>
       <c r="E3">
-        <v>0.45654448775749268</v>
+        <v>0.4565444892870365</v>
       </c>
       <c r="F3">
-        <v>0.43397588538772291</v>
+        <v>0.4339758890086778</v>
       </c>
       <c r="G3">
-        <v>0.4772463557480548</v>
+        <v>0.4772463631387304</v>
       </c>
       <c r="H3">
-        <v>0.45997334139559409</v>
+        <v>0.459973347565318</v>
       </c>
       <c r="I3">
-        <v>0.44758872263886551</v>
+        <v>0.4475887269507726</v>
       </c>
       <c r="J3">
-        <v>0.43853130189562578</v>
+        <v>0.4385313029788988</v>
       </c>
       <c r="K3">
-        <v>0.4132138321874414</v>
+        <v>0.413213835777431</v>
       </c>
       <c r="L3">
-        <v>0.3759152783845956</v>
+        <v>0.3759152845930175</v>
       </c>
       <c r="M3">
-        <v>0.33415669615215199</v>
+        <v>0.334156693292087</v>
       </c>
       <c r="N3">
-        <v>0.30254457201970503</v>
+        <v>0.3025445946123805</v>
       </c>
       <c r="O3">
-        <v>0.28017441092068363</v>
+        <v>0.2801744118257944</v>
       </c>
       <c r="P3">
-        <v>0.26810451550667269</v>
+        <v>0.2681045179348041</v>
       </c>
       <c r="Q3">
-        <v>0.27884258435359288</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
+        <v>0.2788425899382731</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>0.34462329867497071</v>
+        <v>0.344623298893932</v>
       </c>
       <c r="D4">
-        <v>0.42222224383445428</v>
+        <v>0.4222222439872307</v>
       </c>
       <c r="E4">
-        <v>0.43294145100678438</v>
+        <v>0.4329414514310643</v>
       </c>
       <c r="F4">
-        <v>0.45305628569257811</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.50306956449696294</v>
+        <v>0.4530562857153808</v>
+      </c>
+      <c r="G4">
+        <v>0.5030695637885868</v>
       </c>
       <c r="H4">
-        <v>0.55899822952558498</v>
+        <v>0.5589982286972445</v>
       </c>
       <c r="I4">
-        <v>0.56117242781641452</v>
+        <v>0.5611724288974098</v>
       </c>
       <c r="J4">
-        <v>0.56180596334243682</v>
+        <v>0.5618059655979892</v>
       </c>
       <c r="K4">
-        <v>0.52612680660921229</v>
+        <v>0.5261268102356607</v>
       </c>
       <c r="L4">
-        <v>0.49018562390830522</v>
+        <v>0.4901856289783671</v>
       </c>
       <c r="M4">
-        <v>0.46818410449981313</v>
+        <v>0.4681841100520923</v>
       </c>
       <c r="N4">
-        <v>0.39922549042022087</v>
+        <v>0.3992254938803126</v>
       </c>
       <c r="O4">
-        <v>0.33495309253413441</v>
+        <v>0.3349530932925053</v>
       </c>
       <c r="P4">
-        <v>0.28982552911669962</v>
+        <v>0.2898255249961447</v>
       </c>
       <c r="Q4">
-        <v>0.25976334018402158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
+        <v>0.2597633293980917</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.45923263792619018</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C5">
+        <v>0.4592326384092302</v>
       </c>
       <c r="D5">
-        <v>0.44178535808183411</v>
+        <v>0.4417853592139075</v>
       </c>
       <c r="E5">
-        <v>0.4445753498912674</v>
+        <v>0.4445753517794768</v>
       </c>
       <c r="F5">
-        <v>0.45839780481502351</v>
+        <v>0.4583978050675471</v>
       </c>
       <c r="G5">
-        <v>0.50004637145206587</v>
+        <v>0.500046374734148</v>
       </c>
       <c r="H5">
-        <v>0.51306454726577011</v>
+        <v>0.5130645489016288</v>
       </c>
       <c r="I5">
-        <v>0.51221137895306379</v>
+        <v>0.5122113811572723</v>
       </c>
       <c r="J5">
-        <v>0.50189336823935637</v>
+        <v>0.5018933673706172</v>
       </c>
       <c r="K5">
-        <v>0.45969249355465053</v>
+        <v>0.4596924985118652</v>
       </c>
       <c r="L5">
-        <v>0.4178781872410442</v>
+        <v>0.4178781797219097</v>
       </c>
       <c r="M5">
-        <v>0.38921775398777769</v>
+        <v>0.3892177339625808</v>
       </c>
       <c r="N5">
-        <v>0.38369464078680582</v>
+        <v>0.383694609512967</v>
       </c>
       <c r="O5">
-        <v>0.39449902380865098</v>
+        <v>0.3944989876728262</v>
       </c>
       <c r="P5">
-        <v>0.38463554199411099</v>
+        <v>0.3846354945191605</v>
       </c>
       <c r="Q5">
-        <v>0.37624454369130622</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
+        <v>0.3762444841274053</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C6" s="2">
-        <v>0.46126959984815719</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C6">
+        <v>0.4612696001095587</v>
       </c>
       <c r="D6">
-        <v>0.45065673732499711</v>
+        <v>0.4506567377888441</v>
       </c>
       <c r="E6">
-        <v>0.45981737623199581</v>
+        <v>0.4598173773188823</v>
       </c>
       <c r="F6">
-        <v>0.48253373002408312</v>
+        <v>0.4825337295633878</v>
       </c>
       <c r="G6">
-        <v>0.5368566203749342</v>
+        <v>0.5368566205181949</v>
       </c>
       <c r="H6">
-        <v>0.51870865333926763</v>
+        <v>0.5187086495820296</v>
       </c>
       <c r="I6">
-        <v>0.53371350742454648</v>
+        <v>0.5337135036672799</v>
       </c>
       <c r="J6">
-        <v>0.50999086984746556</v>
+        <v>0.5099908561043351</v>
       </c>
       <c r="K6">
-        <v>0.46889058057408828</v>
+        <v>0.4688905672424332</v>
       </c>
       <c r="L6">
-        <v>0.45785648307402521</v>
+        <v>0.457856460114515</v>
       </c>
       <c r="M6">
-        <v>0.43110237144135788</v>
+        <v>0.4311023370267808</v>
       </c>
       <c r="N6">
-        <v>0.41877048639298031</v>
+        <v>0.418770436160592</v>
       </c>
       <c r="O6">
-        <v>0.39317313031481438</v>
+        <v>0.3931730441708363</v>
       </c>
       <c r="P6">
-        <v>0.38256479713759911</v>
+        <v>0.382564687734866</v>
       </c>
       <c r="Q6">
-        <v>0.3586522440638969</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>22</v>
+        <v>0.3586520968093819</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>0.34629163039765642</v>
+        <v>0.3462916306267795</v>
       </c>
       <c r="D7">
-        <v>0.44527718466610922</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0.52146672602636479</v>
+        <v>0.445277184943583</v>
+      </c>
+      <c r="E7">
+        <v>0.521466726495922</v>
       </c>
       <c r="F7">
-        <v>0.54820040954620419</v>
+        <v>0.5482004101754021</v>
       </c>
       <c r="G7">
-        <v>0.57729277710620497</v>
+        <v>0.5772927772291914</v>
       </c>
       <c r="H7">
-        <v>0.5957718712967639</v>
+        <v>0.5957718708628306</v>
       </c>
       <c r="I7">
-        <v>0.59802147821896334</v>
+        <v>0.5980214778395139</v>
       </c>
       <c r="J7">
-        <v>0.60879107345864691</v>
+        <v>0.608791073630756</v>
       </c>
       <c r="K7">
-        <v>0.60526136708805445</v>
+        <v>0.6052613672967736</v>
       </c>
       <c r="L7">
-        <v>0.57402474047264707</v>
+        <v>0.5740247445707433</v>
       </c>
       <c r="M7">
-        <v>0.5480988840747173</v>
+        <v>0.5480988909654643</v>
       </c>
       <c r="N7">
-        <v>0.53200188063082143</v>
+        <v>0.5320018854220441</v>
       </c>
       <c r="O7">
-        <v>0.4612626735045543</v>
+        <v>0.4612626714490763</v>
       </c>
       <c r="P7">
-        <v>0.38930158914083451</v>
+        <v>0.3893015836270766</v>
       </c>
       <c r="Q7">
-        <v>0.34471121593062981</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>23</v>
+        <v>0.3447112018402237</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>0.38960023812574818</v>
+        <v>0.3896002379501451</v>
       </c>
       <c r="D8">
-        <v>0.43121198858315568</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.51492560539789878</v>
+        <v>0.4312119885028855</v>
+      </c>
+      <c r="E8">
+        <v>0.5149256061844392</v>
       </c>
       <c r="F8">
-        <v>0.54925254924705669</v>
+        <v>0.5492525496376166</v>
       </c>
       <c r="G8">
-        <v>0.5558214164160129</v>
+        <v>0.5558214164853139</v>
       </c>
       <c r="H8">
-        <v>0.56677813966175039</v>
+        <v>0.5667781391449754</v>
       </c>
       <c r="I8">
-        <v>0.57372651395902763</v>
+        <v>0.5737265147318737</v>
       </c>
       <c r="J8">
-        <v>0.55762665519924293</v>
+        <v>0.5576266541859147</v>
       </c>
       <c r="K8">
-        <v>0.51430508063791236</v>
+        <v>0.5143050773147528</v>
       </c>
       <c r="L8">
-        <v>0.45255755176354961</v>
+        <v>0.4525575524469057</v>
       </c>
       <c r="M8">
-        <v>0.41908449995126817</v>
+        <v>0.419084496413489</v>
       </c>
       <c r="N8">
-        <v>0.38782388695636261</v>
+        <v>0.3878238787043304</v>
       </c>
       <c r="O8">
-        <v>0.32166032655233368</v>
+        <v>0.3216603187956169</v>
       </c>
       <c r="P8">
-        <v>0.27722805111068111</v>
+        <v>0.2772280538167116</v>
       </c>
       <c r="Q8">
-        <v>0.2087249587536637</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>24</v>
+        <v>0.2087249728826144</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>0.38963014635239651</v>
+        <v>0.3896301461777064</v>
       </c>
       <c r="D9">
-        <v>0.43368249866965408</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.51778288365461078</v>
+        <v>0.4336824986013073</v>
+      </c>
+      <c r="E9">
+        <v>0.517782884478751</v>
       </c>
       <c r="F9">
-        <v>0.55135992963122671</v>
+        <v>0.5513599298533584</v>
       </c>
       <c r="G9">
-        <v>0.55658212171062504</v>
+        <v>0.5565821217718827</v>
       </c>
       <c r="H9">
-        <v>0.56947702648226139</v>
+        <v>0.569477025237407</v>
       </c>
       <c r="I9">
-        <v>0.58208859341231578</v>
+        <v>0.5820885932603067</v>
       </c>
       <c r="J9">
-        <v>0.57544843513832544</v>
+        <v>0.5754484337504526</v>
       </c>
       <c r="K9">
-        <v>0.56441643606944869</v>
+        <v>0.5644164338697096</v>
       </c>
       <c r="L9">
-        <v>0.53246153369377303</v>
+        <v>0.5324615323288823</v>
       </c>
       <c r="M9">
-        <v>0.50128274879081103</v>
+        <v>0.5012827393089354</v>
       </c>
       <c r="N9">
-        <v>0.46977781706781763</v>
+        <v>0.469777792468787</v>
       </c>
       <c r="O9">
-        <v>0.42637952248196459</v>
+        <v>0.426379480380359</v>
       </c>
       <c r="P9">
-        <v>0.41338235723707989</v>
+        <v>0.4133823059723924</v>
       </c>
       <c r="Q9">
-        <v>0.39396876786229013</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>25</v>
+        <v>0.3939687132781831</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>0.39217442036306732</v>
+        <v>0.3921744201853227</v>
       </c>
       <c r="D10">
-        <v>0.4346576462990151</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.51455081916065948</v>
+        <v>0.4346576462225858</v>
+      </c>
+      <c r="E10">
+        <v>0.5145508199225609</v>
       </c>
       <c r="F10">
-        <v>0.54767734408590918</v>
+        <v>0.5476773442593514</v>
       </c>
       <c r="G10">
-        <v>0.55308352590886645</v>
+        <v>0.5530835258649983</v>
       </c>
       <c r="H10">
-        <v>0.56673038141230203</v>
+        <v>0.5667303797692254</v>
       </c>
       <c r="I10">
-        <v>0.58253104695211755</v>
+        <v>0.5825310462628189</v>
       </c>
       <c r="J10">
-        <v>0.57414879074883107</v>
+        <v>0.5741487891248577</v>
       </c>
       <c r="K10">
-        <v>0.56370852334708044</v>
+        <v>0.5637085238378671</v>
       </c>
       <c r="L10">
-        <v>0.53348286633561692</v>
+        <v>0.5334828628312486</v>
       </c>
       <c r="M10">
-        <v>0.50393846643370033</v>
+        <v>0.5039384571605581</v>
       </c>
       <c r="N10">
-        <v>0.47325682495215932</v>
+        <v>0.4732568010043032</v>
       </c>
       <c r="O10">
-        <v>0.43710724786507871</v>
+        <v>0.4371072094942494</v>
       </c>
       <c r="P10">
-        <v>0.42462235016278832</v>
+        <v>0.4246223023772169</v>
       </c>
       <c r="Q10">
-        <v>0.39773307033700961</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
+        <v>0.3977330102429044</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>0.38815531095508998</v>
+        <v>0.3881553107736718</v>
       </c>
       <c r="D11">
-        <v>0.4321419688507257</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0.5128052898144505</v>
+        <v>0.4321419687654221</v>
+      </c>
+      <c r="E11">
+        <v>0.5128052905161788</v>
       </c>
       <c r="F11">
-        <v>0.54658778673596875</v>
+        <v>0.5465877868461507</v>
       </c>
       <c r="G11">
-        <v>0.55310699837241073</v>
+        <v>0.5531069980960586</v>
       </c>
       <c r="H11">
-        <v>0.56601524468272857</v>
+        <v>0.566015242967429</v>
       </c>
       <c r="I11">
-        <v>0.57676395120828639</v>
+        <v>0.5767639507161982</v>
       </c>
       <c r="J11">
-        <v>0.57139219043320499</v>
+        <v>0.5713921883372625</v>
       </c>
       <c r="K11">
-        <v>0.55977372559539296</v>
+        <v>0.5597737219962299</v>
       </c>
       <c r="L11">
-        <v>0.52527434688728258</v>
+        <v>0.5252743427036788</v>
       </c>
       <c r="M11">
-        <v>0.50039644492514801</v>
+        <v>0.500396433882791</v>
       </c>
       <c r="N11">
-        <v>0.474465664614796</v>
+        <v>0.4744656394591092</v>
       </c>
       <c r="O11">
-        <v>0.44352154482119321</v>
+        <v>0.4435215077352709</v>
       </c>
       <c r="P11">
-        <v>0.44084281447265999</v>
+        <v>0.4408427746434223</v>
       </c>
       <c r="Q11">
-        <v>0.4111022119392902</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>27</v>
+        <v>0.4111021688535523</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.47775457594463527</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C12">
+        <v>0.4777545765401622</v>
       </c>
       <c r="D12">
-        <v>0.46550269735093741</v>
+        <v>0.4655026990299587</v>
       </c>
       <c r="E12">
-        <v>0.49521282297204278</v>
+        <v>0.4952128238219449</v>
       </c>
       <c r="F12">
-        <v>0.5141195916602973</v>
+        <v>0.5141195927193255</v>
       </c>
       <c r="G12">
-        <v>0.55999182446539364</v>
+        <v>0.5599918275769167</v>
       </c>
       <c r="H12">
-        <v>0.566745815465861</v>
+        <v>0.5667458171703399</v>
       </c>
       <c r="I12">
-        <v>0.57147475890465493</v>
+        <v>0.5714747626345137</v>
       </c>
       <c r="J12">
-        <v>0.54787521471638767</v>
+        <v>0.5478752199923644</v>
       </c>
       <c r="K12">
-        <v>0.51604120770028372</v>
+        <v>0.5160412105367825</v>
       </c>
       <c r="L12">
-        <v>0.45215382949213112</v>
+        <v>0.4521538247756253</v>
       </c>
       <c r="M12">
-        <v>0.40851827714339889</v>
+        <v>0.4085182763714245</v>
       </c>
       <c r="N12">
-        <v>0.3711239118321667</v>
+        <v>0.3711239118453915</v>
       </c>
       <c r="O12">
-        <v>0.3673099049831629</v>
+        <v>0.3673099054242752</v>
       </c>
       <c r="P12">
-        <v>0.34023524399048649</v>
+        <v>0.3402352397612315</v>
       </c>
       <c r="Q12">
-        <v>0.29058928105772902</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
+        <v>0.2905892760162589</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.47631556314639167</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C13">
+        <v>0.4763155635147402</v>
       </c>
       <c r="D13">
-        <v>0.45310653466335238</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0.49322985773446892</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0.51508912570245513</v>
+        <v>0.4531065350331205</v>
+      </c>
+      <c r="E13">
+        <v>0.493229857714847</v>
+      </c>
+      <c r="F13">
+        <v>0.5150891228921706</v>
       </c>
       <c r="G13">
-        <v>0.48182287367946358</v>
+        <v>0.4818228665170602</v>
       </c>
       <c r="H13">
-        <v>0.49634659199085118</v>
+        <v>0.4963465860438386</v>
       </c>
       <c r="I13">
-        <v>0.51044015834722889</v>
+        <v>0.5104401537608905</v>
       </c>
       <c r="J13">
-        <v>0.50290809268243686</v>
+        <v>0.5029080939458513</v>
       </c>
       <c r="K13">
-        <v>0.47620023328918659</v>
+        <v>0.4762002519368102</v>
       </c>
       <c r="L13">
-        <v>0.40783889165423381</v>
+        <v>0.407838919203343</v>
       </c>
       <c r="M13">
-        <v>0.36083562216384379</v>
+        <v>0.3608356562254716</v>
       </c>
       <c r="N13">
-        <v>0.34362744098522707</v>
+        <v>0.3436274753835467</v>
       </c>
       <c r="O13">
-        <v>0.3062131404985256</v>
+        <v>0.3062131815717586</v>
       </c>
       <c r="P13">
-        <v>0.27163751766411098</v>
+        <v>0.2716375790229423</v>
       </c>
       <c r="Q13">
-        <v>0.22273414080310211</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>29</v>
+        <v>0.222734232028454</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>0.3471633191950485</v>
+        <v>0.3471633194177034</v>
       </c>
       <c r="D14">
-        <v>0.44657945624017031</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0.52484952645434335</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0.54869053021255088</v>
+        <v>0.4465794565114755</v>
+      </c>
+      <c r="E14">
+        <v>0.5248495269671206</v>
+      </c>
+      <c r="F14">
+        <v>0.5486905308274006</v>
       </c>
       <c r="G14">
-        <v>0.57893793942886473</v>
+        <v>0.5789379393505059</v>
       </c>
       <c r="H14">
-        <v>0.59887610807733249</v>
+        <v>0.5988761073784246</v>
       </c>
       <c r="I14">
-        <v>0.60096539763784362</v>
+        <v>0.6009653966202189</v>
       </c>
       <c r="J14">
-        <v>0.61301842392082728</v>
+        <v>0.6130184236081092</v>
       </c>
       <c r="K14">
-        <v>0.61271451295938184</v>
+        <v>0.6127145129236664</v>
       </c>
       <c r="L14">
-        <v>0.59738533955505824</v>
+        <v>0.5973853413746939</v>
       </c>
       <c r="M14">
-        <v>0.58740559992838859</v>
+        <v>0.5874056037401351</v>
       </c>
       <c r="N14">
-        <v>0.57931940561909612</v>
+        <v>0.5793194063991222</v>
       </c>
       <c r="O14">
-        <v>0.53008518952840722</v>
+        <v>0.5300851772338282</v>
       </c>
       <c r="P14">
-        <v>0.48752040974313909</v>
+        <v>0.4875203957123965</v>
       </c>
       <c r="Q14">
-        <v>0.45782849032171619</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>30</v>
+        <v>0.4578284757175374</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>0.34682399913660361</v>
+        <v>0.346823999359971</v>
       </c>
       <c r="D15">
-        <v>0.4456824121947367</v>
+        <v>0.4456824124583311</v>
       </c>
       <c r="E15">
-        <v>0.52284197988324732</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.54658254339584011</v>
+        <v>0.5228419803529485</v>
+      </c>
+      <c r="F15">
+        <v>0.5465825439829786</v>
       </c>
       <c r="G15">
-        <v>0.57750921394537136</v>
+        <v>0.577509213864504</v>
       </c>
       <c r="H15">
-        <v>0.59433174018802859</v>
+        <v>0.5943317394445709</v>
       </c>
       <c r="I15">
-        <v>0.59890711865209845</v>
+        <v>0.5989071176885202</v>
       </c>
       <c r="J15">
-        <v>0.61286015410824712</v>
+        <v>0.6128601531673595</v>
       </c>
       <c r="K15">
-        <v>0.61367789991027866</v>
+        <v>0.6136778990259879</v>
       </c>
       <c r="L15">
-        <v>0.59987329251186661</v>
+        <v>0.5998732935987551</v>
       </c>
       <c r="M15">
-        <v>0.59000227527706972</v>
+        <v>0.5900022778252099</v>
       </c>
       <c r="N15">
-        <v>0.58035517078103549</v>
+        <v>0.5803551706900791</v>
       </c>
       <c r="O15">
-        <v>0.5130179657865287</v>
+        <v>0.5130179530860112</v>
       </c>
       <c r="P15">
-        <v>0.47189060292072649</v>
+        <v>0.4718905892613603</v>
       </c>
       <c r="Q15">
-        <v>0.47193016684353789</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>31</v>
+        <v>0.4719301449418351</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>0.34984097117115209</v>
+        <v>0.3498409713800256</v>
       </c>
       <c r="D16">
-        <v>0.44909316387222531</v>
+        <v>0.4490931641053714</v>
       </c>
       <c r="E16">
-        <v>0.52607527580555913</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0.54945407407597724</v>
+        <v>0.5260752762507306</v>
+      </c>
+      <c r="F16">
+        <v>0.5494540746184959</v>
       </c>
       <c r="G16">
-        <v>0.58187724333505875</v>
+        <v>0.5818772434032712</v>
       </c>
       <c r="H16">
-        <v>0.60149688661358058</v>
+        <v>0.6014968860566094</v>
       </c>
       <c r="I16">
-        <v>0.60632287455199496</v>
+        <v>0.6063228739408387</v>
       </c>
       <c r="J16">
-        <v>0.61789323957240105</v>
+        <v>0.6178932381166959</v>
       </c>
       <c r="K16">
-        <v>0.61976844865561598</v>
+        <v>0.6197684466116886</v>
       </c>
       <c r="L16">
-        <v>0.60804130870792028</v>
+        <v>0.6080413100226497</v>
       </c>
       <c r="M16">
-        <v>0.59812315887295764</v>
+        <v>0.5981231616477647</v>
       </c>
       <c r="N16">
-        <v>0.58662661908181168</v>
+        <v>0.5866266201375655</v>
       </c>
       <c r="O16">
-        <v>0.51207330201076073</v>
+        <v>0.5120732889114409</v>
       </c>
       <c r="P16">
-        <v>0.46598738213802682</v>
+        <v>0.465987368272744</v>
       </c>
       <c r="Q16">
-        <v>0.46815277746250128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>32</v>
+        <v>0.4681527611646202</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>0.34984834815455279</v>
+        <v>0.3498483483782294</v>
       </c>
       <c r="D17">
-        <v>0.44853404999522839</v>
+        <v>0.4485340502697138</v>
       </c>
       <c r="E17">
-        <v>0.52868576387676391</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.55240799923539319</v>
+        <v>0.528685764264759</v>
+      </c>
+      <c r="F17">
+        <v>0.5524079997611226</v>
       </c>
       <c r="G17">
-        <v>0.58263845804663605</v>
+        <v>0.5826384580150782</v>
       </c>
       <c r="H17">
-        <v>0.60074888869482146</v>
+        <v>0.6007488881432852</v>
       </c>
       <c r="I17">
-        <v>0.60454625081066593</v>
+        <v>0.6045462501163291</v>
       </c>
       <c r="J17">
-        <v>0.61810792823683869</v>
+        <v>0.61810792793706</v>
       </c>
       <c r="K17">
-        <v>0.61884683377259031</v>
+        <v>0.6188468338369214</v>
       </c>
       <c r="L17">
-        <v>0.60688886597734459</v>
+        <v>0.6068888673359332</v>
       </c>
       <c r="M17">
-        <v>0.5966941779165571</v>
+        <v>0.5966941806175176</v>
       </c>
       <c r="N17">
-        <v>0.58686539599773779</v>
+        <v>0.5868653961453525</v>
       </c>
       <c r="O17">
-        <v>0.51898785449618279</v>
+        <v>0.5189878406955211</v>
       </c>
       <c r="P17">
-        <v>0.46876840416129922</v>
+        <v>0.4687683891935089</v>
       </c>
       <c r="Q17">
-        <v>0.46827147433233929</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>33</v>
+        <v>0.4682714554734809</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C18" s="2">
-        <v>0.47613832716807442</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C18">
+        <v>0.4761383277182948</v>
       </c>
       <c r="D18">
-        <v>0.45210332159737399</v>
+        <v>0.4521033239333704</v>
       </c>
       <c r="E18">
-        <v>0.48106758443574288</v>
+        <v>0.4810675858150548</v>
       </c>
       <c r="F18">
-        <v>0.4953020308746538</v>
+        <v>0.4953020313857251</v>
       </c>
       <c r="G18">
-        <v>0.54763390920390487</v>
+        <v>0.5476339114972343</v>
       </c>
       <c r="H18">
-        <v>0.54368395540735881</v>
+        <v>0.5436839593592728</v>
       </c>
       <c r="I18">
-        <v>0.56007725768397321</v>
+        <v>0.5600772597479752</v>
       </c>
       <c r="J18">
-        <v>0.54466667850835482</v>
+        <v>0.5446666838139483</v>
       </c>
       <c r="K18">
-        <v>0.52042402684121625</v>
+        <v>0.5204240159188376</v>
       </c>
       <c r="L18">
-        <v>0.47376444082609992</v>
+        <v>0.4737644380267205</v>
       </c>
       <c r="M18">
-        <v>0.44350065698835411</v>
+        <v>0.4435006515130904</v>
       </c>
       <c r="N18">
-        <v>0.43382539465144337</v>
+        <v>0.4338253810427484</v>
       </c>
       <c r="O18">
-        <v>0.44991108506811728</v>
+        <v>0.4499110688160192</v>
       </c>
       <c r="P18">
-        <v>0.44155668781532342</v>
+        <v>0.4415566681712431</v>
       </c>
       <c r="Q18">
-        <v>0.42485758971698317</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>34</v>
+        <v>0.4248575741130619</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>0.47688620849937419</v>
+        <v>0.4768862088209468</v>
       </c>
       <c r="D19">
-        <v>0.45980226142842312</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0.49576754432854481</v>
+        <v>0.4598022622321212</v>
+      </c>
+      <c r="E19">
+        <v>0.4957675448018599</v>
       </c>
       <c r="F19">
-        <v>0.52140329232392746</v>
+        <v>0.5214032915767625</v>
       </c>
       <c r="G19">
-        <v>0.57274381518473305</v>
+        <v>0.5727438219986516</v>
       </c>
       <c r="H19">
-        <v>0.55896048046139946</v>
+        <v>0.5589604797519973</v>
       </c>
       <c r="I19">
-        <v>0.57441981871010672</v>
+        <v>0.5744198177170091</v>
       </c>
       <c r="J19">
-        <v>0.56281500340079249</v>
+        <v>0.5628150007644928</v>
       </c>
       <c r="K19">
-        <v>0.52818060118478982</v>
+        <v>0.5281805928080544</v>
       </c>
       <c r="L19">
-        <v>0.51438282869912921</v>
+        <v>0.514382814516513</v>
       </c>
       <c r="M19">
-        <v>0.47764128533971018</v>
+        <v>0.4776412579784337</v>
       </c>
       <c r="N19">
-        <v>0.46889030643651708</v>
+        <v>0.4688902714029207</v>
       </c>
       <c r="O19">
-        <v>0.44596559010342351</v>
+        <v>0.445965533507018</v>
       </c>
       <c r="P19">
-        <v>0.43121402772576589</v>
+        <v>0.4312139517731651</v>
       </c>
       <c r="Q19">
-        <v>0.3925658715920195</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
+        <v>0.3925657671972467</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>0.47740334262619338</v>
+        <v>0.4774033428751212</v>
       </c>
       <c r="D20">
-        <v>0.47453665451179239</v>
+        <v>0.4745366549911695</v>
       </c>
       <c r="E20">
-        <v>0.50360160506405827</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0.55374076341220801</v>
+        <v>0.5036016056981755</v>
+      </c>
+      <c r="F20">
+        <v>0.5537407634425486</v>
       </c>
       <c r="G20">
-        <v>0.57435075861593121</v>
+        <v>0.5743507584954309</v>
       </c>
       <c r="H20">
-        <v>0.58696684920407549</v>
+        <v>0.5869668488768015</v>
       </c>
       <c r="I20">
-        <v>0.57543406050923662</v>
+        <v>0.5754340544576245</v>
       </c>
       <c r="J20">
-        <v>0.56897517706826806</v>
+        <v>0.5689751747340303</v>
       </c>
       <c r="K20">
-        <v>0.5422069223287298</v>
+        <v>0.5422069138365621</v>
       </c>
       <c r="L20">
-        <v>0.52493705290697568</v>
+        <v>0.524937032838929</v>
       </c>
       <c r="M20">
-        <v>0.50345171550431767</v>
+        <v>0.5034516885255179</v>
       </c>
       <c r="N20">
-        <v>0.49149474535293519</v>
+        <v>0.4914947036727</v>
       </c>
       <c r="O20">
-        <v>0.47931808744152399</v>
+        <v>0.4793180357404626</v>
       </c>
       <c r="P20">
-        <v>0.44600114309611238</v>
+        <v>0.4460010609460037</v>
       </c>
       <c r="Q20">
-        <v>0.39794676544523722</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>36</v>
+        <v>0.3979467281949604</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C21" s="2">
-        <v>0.37734999613982201</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C21">
+        <v>0.3773499899824804</v>
       </c>
       <c r="D21">
-        <v>0.46448061316788142</v>
+        <v>0.4644806144004077</v>
       </c>
       <c r="E21">
-        <v>0.46021592591132943</v>
+        <v>0.4602159271347556</v>
       </c>
       <c r="F21">
-        <v>0.44266086633088969</v>
+        <v>0.4426608690081041</v>
       </c>
       <c r="G21">
-        <v>0.48409126813622078</v>
+        <v>0.4840912725719711</v>
       </c>
       <c r="H21">
-        <v>0.46008521783399459</v>
+        <v>0.4600852206500359</v>
       </c>
       <c r="I21">
-        <v>0.39661848150608608</v>
+        <v>0.3966184900472243</v>
       </c>
       <c r="J21">
-        <v>0.37675544684778189</v>
+        <v>0.3767554513625883</v>
       </c>
       <c r="K21">
-        <v>0.36443711555040031</v>
+        <v>0.3644370987581547</v>
       </c>
       <c r="L21">
-        <v>0.35244122809262202</v>
+        <v>0.3524412326427108</v>
       </c>
       <c r="M21">
-        <v>0.3139451395186138</v>
+        <v>0.3139451112792965</v>
       </c>
       <c r="N21">
-        <v>0.30737222829469552</v>
+        <v>0.3073722114522938</v>
       </c>
       <c r="O21">
-        <v>0.30588652474521782</v>
+        <v>0.3058865073405383</v>
       </c>
       <c r="P21">
-        <v>0.30155398258533661</v>
+        <v>0.3015539626263368</v>
       </c>
       <c r="Q21">
-        <v>0.28312613947479559</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>37</v>
+        <v>0.2831261130914667</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0.36888338570805551</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.46260265450439059</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C22">
+        <v>0.3688833794130933</v>
+      </c>
+      <c r="D22">
+        <v>0.4626026552679839</v>
       </c>
       <c r="E22">
-        <v>0.45648851992502171</v>
+        <v>0.4564885197247038</v>
       </c>
       <c r="F22">
-        <v>0.43080644476415758</v>
+        <v>0.4308064386040382</v>
       </c>
       <c r="G22">
-        <v>0.48368085738977318</v>
+        <v>0.4836808512259578</v>
       </c>
       <c r="H22">
-        <v>0.4680353685036186</v>
+        <v>0.4680353656198049</v>
       </c>
       <c r="I22">
-        <v>0.41120678244684949</v>
+        <v>0.4112067661380389</v>
       </c>
       <c r="J22">
-        <v>0.38646750694812348</v>
+        <v>0.386467474968585</v>
       </c>
       <c r="K22">
-        <v>0.34230318571276652</v>
+        <v>0.3423031348364304</v>
       </c>
       <c r="L22">
-        <v>0.34629878853334822</v>
+        <v>0.3462986932910481</v>
       </c>
       <c r="M22">
-        <v>0.31921826918717588</v>
+        <v>0.3192181507124329</v>
       </c>
       <c r="N22">
-        <v>0.31564077568835042</v>
+        <v>0.3156406381494538</v>
       </c>
       <c r="O22">
-        <v>0.32247862424354751</v>
+        <v>0.3224784641589815</v>
       </c>
       <c r="P22">
-        <v>0.31986633818530491</v>
+        <v>0.3198661558851104</v>
       </c>
       <c r="Q22">
-        <v>0.28078956846466657</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>38</v>
+        <v>0.2807893534414925</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C23" s="2">
-        <v>0.47257300397731872</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C23">
+        <v>0.4725730051192584</v>
       </c>
       <c r="D23">
-        <v>0.47409947156705229</v>
+        <v>0.4740994730863287</v>
       </c>
       <c r="E23">
-        <v>0.4744945683005497</v>
+        <v>0.4744945674571031</v>
       </c>
       <c r="F23">
-        <v>0.48911238289570902</v>
+        <v>0.4891123858976124</v>
       </c>
       <c r="G23">
-        <v>0.43866076364859069</v>
+        <v>0.4386607845520659</v>
       </c>
       <c r="H23">
-        <v>0.44534759629083498</v>
+        <v>0.4453476144075372</v>
       </c>
       <c r="I23">
-        <v>0.37257627890365302</v>
+        <v>0.3725762818639097</v>
       </c>
       <c r="J23">
-        <v>0.34567309708962779</v>
+        <v>0.3456730699491813</v>
       </c>
       <c r="K23">
-        <v>0.32909040599299422</v>
+        <v>0.3290903466516505</v>
       </c>
       <c r="L23">
-        <v>0.30786786306159358</v>
+        <v>0.3078677402869066</v>
       </c>
       <c r="M23">
-        <v>0.27047660993352851</v>
+        <v>0.2704764328242805</v>
       </c>
       <c r="N23">
-        <v>0.21353269165917141</v>
+        <v>0.2135324632222488</v>
       </c>
       <c r="O23">
-        <v>0.16943227145006279</v>
+        <v>0.1694320174469979</v>
       </c>
       <c r="P23">
-        <v>0.16794982684388421</v>
+        <v>0.1679495342298294</v>
       </c>
       <c r="Q23">
-        <v>0.1237280764412428</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>39</v>
+        <v>0.1237276150407849</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C24" s="2">
-        <v>0.50835172798685446</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C24">
+        <v>0.5083517280998935</v>
       </c>
       <c r="D24">
-        <v>0.52663191132128473</v>
+        <v>0.5266319115084435</v>
       </c>
       <c r="E24">
-        <v>0.51485809607274602</v>
+        <v>0.5148580970706563</v>
       </c>
       <c r="F24">
-        <v>0.53387594680041961</v>
+        <v>0.5338759473902746</v>
       </c>
       <c r="G24">
-        <v>0.55056356308655796</v>
+        <v>0.5505635618776159</v>
       </c>
       <c r="H24">
-        <v>0.57840015521819121</v>
+        <v>0.5784001521683414</v>
       </c>
       <c r="I24">
-        <v>0.57000473054123779</v>
+        <v>0.5700047270536696</v>
       </c>
       <c r="J24">
-        <v>0.58506898978722743</v>
+        <v>0.5850689808976487</v>
       </c>
       <c r="K24">
-        <v>0.5734665168116132</v>
+        <v>0.573466501310208</v>
       </c>
       <c r="L24">
-        <v>0.55365799790890102</v>
+        <v>0.5536579671911668</v>
       </c>
       <c r="M24">
-        <v>0.51462470426983264</v>
+        <v>0.5146246835319795</v>
       </c>
       <c r="N24">
-        <v>0.44330621033495943</v>
+        <v>0.4433062140378409</v>
       </c>
       <c r="O24">
-        <v>0.412077067359643</v>
+        <v>0.4120771052987435</v>
       </c>
       <c r="P24">
-        <v>0.37754256787697232</v>
+        <v>0.3775426301097537</v>
       </c>
       <c r="Q24">
-        <v>0.34344111908219549</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>40</v>
+        <v>0.3434411837563678</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C25" s="2">
-        <v>0.51250520738056182</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C25">
+        <v>0.5125052074887048</v>
       </c>
       <c r="D25">
-        <v>0.53243960669433443</v>
+        <v>0.5324396068789465</v>
       </c>
       <c r="E25">
-        <v>0.53313139236531448</v>
+        <v>0.5331313932097729</v>
       </c>
       <c r="F25">
-        <v>0.56234933130673526</v>
+        <v>0.5623493314214425</v>
       </c>
       <c r="G25">
-        <v>0.56907088871977074</v>
+        <v>0.5690708883348663</v>
       </c>
       <c r="H25">
-        <v>0.58442924017809694</v>
+        <v>0.584429238570622</v>
       </c>
       <c r="I25">
-        <v>0.57447392466800984</v>
+        <v>0.5744739217490958</v>
       </c>
       <c r="J25">
-        <v>0.56843699290037997</v>
+        <v>0.5684369867996334</v>
       </c>
       <c r="K25">
-        <v>0.59313106185195963</v>
+        <v>0.5931310481713526</v>
       </c>
       <c r="L25">
-        <v>0.60160474131766339</v>
+        <v>0.6016047258816462</v>
       </c>
       <c r="M25">
-        <v>0.56159195316020472</v>
+        <v>0.5615919438615289</v>
       </c>
       <c r="N25">
-        <v>0.53001878330526875</v>
+        <v>0.5300188114610547</v>
       </c>
       <c r="O25">
-        <v>0.46039882270322202</v>
+        <v>0.460398879181564</v>
       </c>
       <c r="P25">
-        <v>0.43324926454108309</v>
+        <v>0.4332493544745926</v>
       </c>
       <c r="Q25">
-        <v>0.40477514778791568</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>41</v>
+        <v>0.4047752611227574</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C26" s="2">
-        <v>0.52333712573828328</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C26">
+        <v>0.5233371257554972</v>
       </c>
       <c r="D26">
-        <v>0.52140296353892956</v>
+        <v>0.5214029636539675</v>
       </c>
       <c r="E26">
-        <v>0.51182704813644853</v>
+        <v>0.5118270481040625</v>
       </c>
       <c r="F26">
-        <v>0.56150859339297576</v>
+        <v>0.5615085924457982</v>
       </c>
       <c r="G26">
-        <v>0.56567990633380871</v>
+        <v>0.5656799053224845</v>
       </c>
       <c r="H26">
-        <v>0.59349210722060952</v>
+        <v>0.5934921045197172</v>
       </c>
       <c r="I26">
-        <v>0.60141352391089553</v>
+        <v>0.6014135193254304</v>
       </c>
       <c r="J26">
-        <v>0.60007875895289675</v>
+        <v>0.6000787514439538</v>
       </c>
       <c r="K26">
-        <v>0.575224912185898</v>
+        <v>0.5752248929995099</v>
       </c>
       <c r="L26">
-        <v>0.5613018395512871</v>
+        <v>0.5613018426809936</v>
       </c>
       <c r="M26">
-        <v>0.50958147655786334</v>
+        <v>0.5095815071221658</v>
       </c>
       <c r="N26">
-        <v>0.46221807381687968</v>
+        <v>0.4622181474178511</v>
       </c>
       <c r="O26">
-        <v>0.45189092690057348</v>
+        <v>0.4518910385563349</v>
       </c>
       <c r="P26">
-        <v>0.40468599000917072</v>
+        <v>0.4046861247418211</v>
       </c>
       <c r="Q26">
-        <v>0.36797567672361958</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>42</v>
+        <v>0.3679758468495893</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C27" s="2">
-        <v>0.52509276042843345</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C27">
+        <v>0.5250927604465691</v>
       </c>
       <c r="D27">
-        <v>0.52346386503868436</v>
+        <v>0.5234638652071669</v>
       </c>
       <c r="E27">
-        <v>0.51424167331887272</v>
+        <v>0.5142416736880794</v>
       </c>
       <c r="F27">
-        <v>0.56526939499958129</v>
+        <v>0.5652693950310491</v>
       </c>
       <c r="G27">
-        <v>0.56546467084100693</v>
+        <v>0.5654646710727048</v>
       </c>
       <c r="H27">
-        <v>0.59469934300521987</v>
+        <v>0.5946993417441591</v>
       </c>
       <c r="I27">
-        <v>0.60171698874241819</v>
+        <v>0.6017169873001558</v>
       </c>
       <c r="J27">
-        <v>0.60513266379052799</v>
+        <v>0.6051326621005073</v>
       </c>
       <c r="K27">
-        <v>0.5943033411895754</v>
+        <v>0.5943033340912887</v>
       </c>
       <c r="L27">
-        <v>0.59540959421465478</v>
+        <v>0.5954095934753908</v>
       </c>
       <c r="M27">
-        <v>0.57744222262823974</v>
+        <v>0.5774422281208924</v>
       </c>
       <c r="N27">
-        <v>0.523548307108613</v>
+        <v>0.5235483250244074</v>
       </c>
       <c r="O27">
-        <v>0.51504335383049293</v>
+        <v>0.5150433878856484</v>
       </c>
       <c r="P27">
-        <v>0.4860608440066494</v>
+        <v>0.4860608902531206</v>
       </c>
       <c r="Q27">
-        <v>0.46887018653679691</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>43</v>
+        <v>0.4688702357254432</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>0.51311772138184653</v>
+        <v>0.5131177214911306</v>
       </c>
       <c r="D28">
-        <v>0.53510322780295372</v>
+        <v>0.535103228020353</v>
       </c>
       <c r="E28">
-        <v>0.53317129029041344</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0.56289234679540989</v>
+        <v>0.5331712913223108</v>
+      </c>
+      <c r="F28">
+        <v>0.5628923473491011</v>
       </c>
       <c r="G28">
-        <v>0.57386615826888487</v>
+        <v>0.5738661572095405</v>
       </c>
       <c r="H28">
-        <v>0.59131037839034484</v>
+        <v>0.5913103783285323</v>
       </c>
       <c r="I28">
-        <v>0.58382193218612943</v>
+        <v>0.5838219318167353</v>
       </c>
       <c r="J28">
-        <v>0.58465461253732776</v>
+        <v>0.5846546047427298</v>
       </c>
       <c r="K28">
-        <v>0.60891053987138122</v>
+        <v>0.6089105339368802</v>
       </c>
       <c r="L28">
-        <v>0.62605931738158316</v>
+        <v>0.6260593158138993</v>
       </c>
       <c r="M28">
-        <v>0.60554572547052032</v>
+        <v>0.6055457211998986</v>
       </c>
       <c r="N28">
-        <v>0.60208085094705921</v>
+        <v>0.6020808546322367</v>
       </c>
       <c r="O28">
-        <v>0.57179687422079073</v>
+        <v>0.5717968816125795</v>
       </c>
       <c r="P28">
-        <v>0.55251247760446631</v>
+        <v>0.5525125017769107</v>
       </c>
       <c r="Q28">
-        <v>0.50012384381564534</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>44</v>
+        <v>0.5001239027458464</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>0.51098227384565775</v>
+        <v>0.5109822739571959</v>
       </c>
       <c r="D29">
-        <v>0.53234875837892193</v>
+        <v>0.5323487586029427</v>
       </c>
       <c r="E29">
-        <v>0.53295765017600572</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0.56039837932277481</v>
+        <v>0.5329576512448887</v>
+      </c>
+      <c r="F29">
+        <v>0.5603983801156737</v>
       </c>
       <c r="G29">
-        <v>0.56888923257561841</v>
+        <v>0.5688892333142157</v>
       </c>
       <c r="H29">
-        <v>0.58531394923169089</v>
+        <v>0.585313949236565</v>
       </c>
       <c r="I29">
-        <v>0.57649183326285658</v>
+        <v>0.5764918326330521</v>
       </c>
       <c r="J29">
-        <v>0.57937415519550506</v>
+        <v>0.5793741474738491</v>
       </c>
       <c r="K29">
-        <v>0.60120245336257094</v>
+        <v>0.6012024063899509</v>
       </c>
       <c r="L29">
-        <v>0.62210250716097126</v>
+        <v>0.6221025015430233</v>
       </c>
       <c r="M29">
-        <v>0.60212602135029281</v>
+        <v>0.602126027917623</v>
       </c>
       <c r="N29">
-        <v>0.60177019520934349</v>
+        <v>0.6017702134686477</v>
       </c>
       <c r="O29">
-        <v>0.57822676454434696</v>
+        <v>0.5782267696191787</v>
       </c>
       <c r="P29">
-        <v>0.56473608555396537</v>
+        <v>0.5647361008642059</v>
       </c>
       <c r="Q29">
-        <v>0.51629959788487889</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>45</v>
+        <v>0.5162996810845845</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>0.51165307005173799</v>
+        <v>0.5116530701619929</v>
       </c>
       <c r="D30">
-        <v>0.53322924799839233</v>
+        <v>0.5332292482237651</v>
       </c>
       <c r="E30">
-        <v>0.53543077759383806</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0.56339995743334337</v>
+        <v>0.5354307785726681</v>
+      </c>
+      <c r="F30">
+        <v>0.5633999580446476</v>
       </c>
       <c r="G30">
-        <v>0.57137027291235443</v>
+        <v>0.5713702731370454</v>
       </c>
       <c r="H30">
-        <v>0.58776641083678582</v>
+        <v>0.5877664109445477</v>
       </c>
       <c r="I30">
-        <v>0.57696815757192266</v>
+        <v>0.5769681574143055</v>
       </c>
       <c r="J30">
-        <v>0.57930876305793044</v>
+        <v>0.5793087635061318</v>
       </c>
       <c r="K30">
-        <v>0.60056997660298306</v>
+        <v>0.6005699721049934</v>
       </c>
       <c r="L30">
-        <v>0.62518636324372978</v>
+        <v>0.6251863618693503</v>
       </c>
       <c r="M30">
-        <v>0.6023724344036322</v>
+        <v>0.6023724279326299</v>
       </c>
       <c r="N30">
-        <v>0.60367583304800199</v>
+        <v>0.6036758319176352</v>
       </c>
       <c r="O30">
-        <v>0.58301738662438962</v>
+        <v>0.5830173932327821</v>
       </c>
       <c r="P30">
-        <v>0.5716092088139878</v>
+        <v>0.5716092378953155</v>
       </c>
       <c r="Q30">
-        <v>0.52469769753141982</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
+        <v>0.5246977462313759</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>0.51030213300842797</v>
+        <v>0.5103021331177452</v>
       </c>
       <c r="D31">
-        <v>0.53091802312976077</v>
+        <v>0.5309180233446782</v>
       </c>
       <c r="E31">
-        <v>0.53066179751330778</v>
-      </c>
-      <c r="F31" s="2">
-        <v>0.56071234554245786</v>
+        <v>0.5306617984517351</v>
+      </c>
+      <c r="F31">
+        <v>0.5607123461372077</v>
       </c>
       <c r="G31">
-        <v>0.57078879945435901</v>
+        <v>0.5707888000024014</v>
       </c>
       <c r="H31">
-        <v>0.58592834517974401</v>
+        <v>0.5859283453980909</v>
       </c>
       <c r="I31">
-        <v>0.57720287743385201</v>
+        <v>0.5772028769589219</v>
       </c>
       <c r="J31">
-        <v>0.57939278679717177</v>
+        <v>0.5793927820830085</v>
       </c>
       <c r="K31">
-        <v>0.59830468566105166</v>
+        <v>0.5983046811922305</v>
       </c>
       <c r="L31">
-        <v>0.62447380305466638</v>
+        <v>0.6244738013255714</v>
       </c>
       <c r="M31">
-        <v>0.60457909450930747</v>
+        <v>0.6045790923381873</v>
       </c>
       <c r="N31">
-        <v>0.6092550184613279</v>
+        <v>0.6092550198696881</v>
       </c>
       <c r="O31">
-        <v>0.59023025155275055</v>
+        <v>0.5902302614314254</v>
       </c>
       <c r="P31">
-        <v>0.58035336171324736</v>
+        <v>0.5803533685577821</v>
       </c>
       <c r="Q31">
-        <v>0.54017146894769275</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>47</v>
+        <v>0.5401714834619002</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>0.51022671492179261</v>
+        <v>0.5102267150307229</v>
       </c>
       <c r="D32">
-        <v>0.53151085283408561</v>
+        <v>0.5315108530395526</v>
       </c>
       <c r="E32">
-        <v>0.52925157595572236</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0.56375400598728409</v>
+        <v>0.5292515768636444</v>
+      </c>
+      <c r="F32">
+        <v>0.5637540064735176</v>
       </c>
       <c r="G32">
-        <v>0.57050483583345846</v>
+        <v>0.5705048358886197</v>
       </c>
       <c r="H32">
-        <v>0.58427266102301489</v>
+        <v>0.584272660866208</v>
       </c>
       <c r="I32">
-        <v>0.57624000211139925</v>
+        <v>0.5762400010567177</v>
       </c>
       <c r="J32">
-        <v>0.57545264045828881</v>
+        <v>0.5754526331558552</v>
       </c>
       <c r="K32">
-        <v>0.60068749873750316</v>
+        <v>0.6006874919437256</v>
       </c>
       <c r="L32">
-        <v>0.62153062647772184</v>
+        <v>0.6215306245613307</v>
       </c>
       <c r="M32">
-        <v>0.59181115838515463</v>
+        <v>0.591811156291106</v>
       </c>
       <c r="N32">
-        <v>0.59065238875774018</v>
+        <v>0.590652398048974</v>
       </c>
       <c r="O32">
-        <v>0.55364668003591111</v>
+        <v>0.553646704961804</v>
       </c>
       <c r="P32">
-        <v>0.5429719999808712</v>
+        <v>0.5429720438004523</v>
       </c>
       <c r="Q32">
-        <v>0.510899546156798</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>48</v>
+        <v>0.5108995971693258</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>0.50967269346092736</v>
+        <v>0.5096726935699877</v>
       </c>
       <c r="D33">
-        <v>0.53096402790951824</v>
+        <v>0.5309640281083693</v>
       </c>
       <c r="E33">
-        <v>0.53379677309867679</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0.56160240169337194</v>
+        <v>0.5337967739568452</v>
+      </c>
+      <c r="F33">
+        <v>0.5616024021942566</v>
       </c>
       <c r="G33">
-        <v>0.57154740602928122</v>
+        <v>0.57154740631683</v>
       </c>
       <c r="H33">
-        <v>0.58544091705715506</v>
+        <v>0.5854409170009324</v>
       </c>
       <c r="I33">
-        <v>0.57988914500147892</v>
+        <v>0.579889144031309</v>
       </c>
       <c r="J33">
-        <v>0.57891217693507824</v>
+        <v>0.5789121706289488</v>
       </c>
       <c r="K33">
-        <v>0.60151793032910716</v>
+        <v>0.6015179248491915</v>
       </c>
       <c r="L33">
-        <v>0.61948379422075428</v>
+        <v>0.6194837932188356</v>
       </c>
       <c r="M33">
-        <v>0.5957918583126075</v>
+        <v>0.5957918558062382</v>
       </c>
       <c r="N33">
-        <v>0.59393683814767506</v>
+        <v>0.5939368392269826</v>
       </c>
       <c r="O33">
-        <v>0.55640979004718261</v>
+        <v>0.5564098071020243</v>
       </c>
       <c r="P33">
-        <v>0.55091764202125915</v>
+        <v>0.5509176690186951</v>
       </c>
       <c r="Q33">
-        <v>0.51617632251891721</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>49</v>
+        <v>0.5161763739419931</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>0.5092845220472263</v>
+        <v>0.5092845221631107</v>
       </c>
       <c r="D34">
-        <v>0.53122294677206461</v>
+        <v>0.5312229469886895</v>
       </c>
       <c r="E34">
-        <v>0.53595877981264939</v>
-      </c>
-      <c r="F34" s="6">
-        <v>0.55958524996746783</v>
+        <v>0.5359587806959752</v>
+      </c>
+      <c r="F34">
+        <v>0.5595852506070275</v>
       </c>
       <c r="G34">
-        <v>0.56866408258553758</v>
+        <v>0.5686640830413736</v>
       </c>
       <c r="H34">
-        <v>0.58209086734196092</v>
+        <v>0.582090866972402</v>
       </c>
       <c r="I34">
-        <v>0.57301806693728519</v>
+        <v>0.5730180665093341</v>
       </c>
       <c r="J34">
-        <v>0.57311204387557013</v>
+        <v>0.5731120381339999</v>
       </c>
       <c r="K34">
-        <v>0.59927609444069962</v>
+        <v>0.5992760884764913</v>
       </c>
       <c r="L34">
-        <v>0.61466602657616654</v>
+        <v>0.6146660232098248</v>
       </c>
       <c r="M34">
-        <v>0.59343971231021264</v>
+        <v>0.59343970715497</v>
       </c>
       <c r="N34">
-        <v>0.5919035981987284</v>
+        <v>0.5919036044006302</v>
       </c>
       <c r="O34">
-        <v>0.55668661921949081</v>
+        <v>0.5566866388270675</v>
       </c>
       <c r="P34">
-        <v>0.55565515151770772</v>
+        <v>0.5556551808439212</v>
       </c>
       <c r="Q34">
-        <v>0.5251642172187948</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>50</v>
+        <v>0.5251642848941068</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>0.51049296905691144</v>
+        <v>0.5104929691665279</v>
       </c>
       <c r="D35">
-        <v>0.53359638034117729</v>
+        <v>0.5335963805628307</v>
       </c>
       <c r="E35">
-        <v>0.53898708969450349</v>
-      </c>
-      <c r="F35" s="5">
-        <v>0.56517797106518797</v>
+        <v>0.5389870905602323</v>
+      </c>
+      <c r="F35">
+        <v>0.565177971443707</v>
       </c>
       <c r="G35">
-        <v>0.57442061528579036</v>
+        <v>0.574420615690712</v>
       </c>
       <c r="H35">
-        <v>0.59275915126008638</v>
+        <v>0.592759151150124</v>
       </c>
       <c r="I35">
-        <v>0.58459882968243693</v>
+        <v>0.5845988294213412</v>
       </c>
       <c r="J35">
-        <v>0.58766245315880916</v>
+        <v>0.5876624472976307</v>
       </c>
       <c r="K35">
-        <v>0.60923093744443668</v>
+        <v>0.6092309325514939</v>
       </c>
       <c r="L35">
-        <v>0.62630014487496388</v>
+        <v>0.6263001441827942</v>
       </c>
       <c r="M35">
-        <v>0.60656314699539238</v>
+        <v>0.6065631447431036</v>
       </c>
       <c r="N35">
-        <v>0.60429971850549058</v>
+        <v>0.6042997222690389</v>
       </c>
       <c r="O35">
-        <v>0.56597890918348548</v>
+        <v>0.565978928526674</v>
       </c>
       <c r="P35">
-        <v>0.55901280406192932</v>
+        <v>0.5590128409661089</v>
       </c>
       <c r="Q35">
-        <v>0.52436899566157702</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>51</v>
+        <v>0.5243690659897473</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>-1.8778932657874E-2</v>
+        <v>-0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>0.51070388724349658</v>
+        <v>0.5107038873603913</v>
       </c>
       <c r="D36">
-        <v>0.5322600882757752</v>
+        <v>0.532260088503729</v>
       </c>
       <c r="E36">
-        <v>0.53359056166796792</v>
-      </c>
-      <c r="F36" s="4">
-        <v>0.56464434708862499</v>
+        <v>0.5335905626327614</v>
+      </c>
+      <c r="F36">
+        <v>0.5646443477048881</v>
       </c>
       <c r="G36">
-        <v>0.57200120562279289</v>
+        <v>0.5720012062689001</v>
       </c>
       <c r="H36">
-        <v>0.58703186123925166</v>
+        <v>0.5870318614340887</v>
       </c>
       <c r="I36">
-        <v>0.57956329412623797</v>
+        <v>0.5795632938658676</v>
       </c>
       <c r="J36">
-        <v>0.58113122545935725</v>
+        <v>0.5811312235775403</v>
       </c>
       <c r="K36">
-        <v>0.6019093663539864</v>
+        <v>0.6019093609076787</v>
       </c>
       <c r="L36">
-        <v>0.62399682538842827</v>
+        <v>0.6239968241025838</v>
       </c>
       <c r="M36">
-        <v>0.60422914000166406</v>
+        <v>0.6042291363818932</v>
       </c>
       <c r="N36">
-        <v>0.60635904750706426</v>
+        <v>0.6063590492748986</v>
       </c>
       <c r="O36">
-        <v>0.58346460471291139</v>
+        <v>0.5834646753874024</v>
       </c>
       <c r="P36">
-        <v>0.57060492218616132</v>
+        <v>0.5706050190418233</v>
       </c>
       <c r="Q36">
-        <v>0.53415747643350231</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>52</v>
+        <v>0.5341575396993732</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>0.53247821131109352</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C37">
+        <v>0.5324782112891501</v>
       </c>
       <c r="D37">
-        <v>0.5405557143202705</v>
+        <v>0.5405557141469319</v>
       </c>
       <c r="E37">
-        <v>0.53980055472907884</v>
+        <v>0.5398005536209367</v>
       </c>
       <c r="F37">
-        <v>0.54334176495727105</v>
+        <v>0.5433417581458014</v>
       </c>
       <c r="G37">
-        <v>0.4883792641086217</v>
+        <v>0.4883792470412735</v>
       </c>
       <c r="H37">
-        <v>0.46953788817997683</v>
+        <v>0.4695378538254225</v>
       </c>
       <c r="I37">
-        <v>0.51198658020259247</v>
+        <v>0.5119865953696096</v>
       </c>
       <c r="J37">
-        <v>0.50590403022792663</v>
+        <v>0.5059040963122632</v>
       </c>
       <c r="K37">
-        <v>0.47952049044748413</v>
+        <v>0.4795205815327546</v>
       </c>
       <c r="L37">
-        <v>0.44348394635366378</v>
+        <v>0.4434840495207877</v>
       </c>
       <c r="M37">
-        <v>0.43952013400827539</v>
+        <v>0.4395202838529734</v>
       </c>
       <c r="N37">
-        <v>0.42070936944724641</v>
+        <v>0.4207095268066935</v>
       </c>
       <c r="O37">
-        <v>0.37623470162542888</v>
+        <v>0.376234865742779</v>
       </c>
       <c r="P37">
-        <v>0.32720614264676962</v>
+        <v>0.3272062804527106</v>
       </c>
       <c r="Q37">
-        <v>0.29825725766137051</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>53</v>
+        <v>0.2982573961881431</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C38" s="4">
-        <v>0.52952506510219333</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C38">
+        <v>0.5295250650592049</v>
       </c>
       <c r="D38">
-        <v>0.54185196587906415</v>
+        <v>0.5418519661541999</v>
       </c>
       <c r="E38">
-        <v>0.54763763563547241</v>
+        <v>0.547637636517557</v>
       </c>
       <c r="F38">
-        <v>0.55324310254142373</v>
+        <v>0.5532431004694073</v>
       </c>
       <c r="G38">
-        <v>0.51827864188343831</v>
+        <v>0.5182786336729782</v>
       </c>
       <c r="H38">
-        <v>0.50755852632593446</v>
+        <v>0.5075585085994483</v>
       </c>
       <c r="I38">
-        <v>0.55290704243510069</v>
+        <v>0.5529070373534372</v>
       </c>
       <c r="J38">
-        <v>0.52028061820544136</v>
+        <v>0.5202806110583369</v>
       </c>
       <c r="K38">
-        <v>0.4991151000117473</v>
+        <v>0.4991150990772856</v>
       </c>
       <c r="L38">
-        <v>0.46917316206225251</v>
+        <v>0.4691731751883489</v>
       </c>
       <c r="M38">
-        <v>0.47820396794797287</v>
+        <v>0.4782039876126376</v>
       </c>
       <c r="N38">
-        <v>0.49111959885500589</v>
+        <v>0.4911196144709294</v>
       </c>
       <c r="O38">
-        <v>0.48352285561303521</v>
+        <v>0.4835228889723219</v>
       </c>
       <c r="P38">
-        <v>0.45081775160739512</v>
+        <v>0.4508177443455019</v>
       </c>
       <c r="Q38">
-        <v>0.45929909235019772</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>54</v>
+        <v>0.4592990596823588</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C39" s="2">
-        <v>0.52812312957730811</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C39">
+        <v>0.5281231295433652</v>
       </c>
       <c r="D39">
-        <v>0.5415121953469445</v>
+        <v>0.5415121956406577</v>
       </c>
       <c r="E39">
-        <v>0.55128485102771563</v>
+        <v>0.5512848519021378</v>
       </c>
       <c r="F39">
-        <v>0.56218998525706987</v>
+        <v>0.5621899840938499</v>
       </c>
       <c r="G39">
-        <v>0.5399476747594848</v>
+        <v>0.5399476694191331</v>
       </c>
       <c r="H39">
-        <v>0.53567446070352565</v>
+        <v>0.5356744498103652</v>
       </c>
       <c r="I39">
-        <v>0.57492538974754981</v>
+        <v>0.5749253853999791</v>
       </c>
       <c r="J39">
-        <v>0.55309366137495719</v>
+        <v>0.5530936542202797</v>
       </c>
       <c r="K39">
-        <v>0.50283348250814364</v>
+        <v>0.5028334715726817</v>
       </c>
       <c r="L39">
-        <v>0.50755828476978504</v>
+        <v>0.5075582836655874</v>
       </c>
       <c r="M39">
-        <v>0.48860799615251832</v>
+        <v>0.4886079978886128</v>
       </c>
       <c r="N39">
-        <v>0.4928678372779125</v>
+        <v>0.4928678812915212</v>
       </c>
       <c r="O39">
-        <v>0.45239562567647801</v>
+        <v>0.4523957348394092</v>
       </c>
       <c r="P39">
-        <v>0.43225094148590842</v>
+        <v>0.4322510764393612</v>
       </c>
       <c r="Q39">
-        <v>0.38579064791389822</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>55</v>
+        <v>0.3857907352284374</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C40" s="2">
-        <v>0.50358415185490579</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C40">
+        <v>0.5035841510839678</v>
       </c>
       <c r="D40">
-        <v>0.50467788369408384</v>
+        <v>0.5046778840793102</v>
       </c>
       <c r="E40">
-        <v>0.50553651054158433</v>
+        <v>0.5055365114505238</v>
       </c>
       <c r="F40">
-        <v>0.50918304415436755</v>
+        <v>0.5091830432657108</v>
       </c>
       <c r="G40">
-        <v>0.50863727748564691</v>
+        <v>0.5086372634720761</v>
       </c>
       <c r="H40">
-        <v>0.47501892270703849</v>
+        <v>0.4750188931623335</v>
       </c>
       <c r="I40">
-        <v>0.38477848402130482</v>
+        <v>0.3847784348127667</v>
       </c>
       <c r="J40">
-        <v>0.34996642523631311</v>
+        <v>0.349966319442964</v>
       </c>
       <c r="K40">
-        <v>0.30679110256289649</v>
+        <v>0.3067910502420484</v>
       </c>
       <c r="L40">
-        <v>0.26847014456914342</v>
+        <v>0.2684701163523369</v>
       </c>
       <c r="M40">
-        <v>0.1975168701049731</v>
+        <v>0.1975167624726782</v>
       </c>
       <c r="N40">
-        <v>0.1004617908069643</v>
+        <v>0.1004615305442208</v>
       </c>
       <c r="O40">
-        <v>-2.674720435096288E-2</v>
+        <v>-0.02674778918118057</v>
       </c>
       <c r="P40">
-        <v>-0.11969128760509951</v>
+        <v>-0.119691878678483</v>
       </c>
       <c r="Q40">
-        <v>-0.147206834119013</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>56</v>
+        <v>-0.1472073046226476</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C41" s="2">
-        <v>0.48008023254360338</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C41">
+        <v>0.4800802339398269</v>
       </c>
       <c r="D41">
-        <v>0.51430664434729101</v>
+        <v>0.514306648127339</v>
       </c>
       <c r="E41">
-        <v>0.47489090564097819</v>
+        <v>0.474890911281119</v>
       </c>
       <c r="F41">
-        <v>0.40783504441844509</v>
+        <v>0.4078350586059697</v>
       </c>
       <c r="G41">
-        <v>0.3467351914904197</v>
+        <v>0.3467352164015092</v>
       </c>
       <c r="H41">
-        <v>0.34038665047875732</v>
+        <v>0.3403866670735869</v>
       </c>
       <c r="I41">
-        <v>0.31946150443047228</v>
+        <v>0.319461507950605</v>
       </c>
       <c r="J41">
-        <v>0.32001791930762002</v>
+        <v>0.3200179055652203</v>
       </c>
       <c r="K41">
-        <v>0.31480591645757039</v>
+        <v>0.3148059161467897</v>
       </c>
       <c r="L41">
-        <v>0.30200807557898879</v>
+        <v>0.3020081001008425</v>
       </c>
       <c r="M41">
-        <v>0.27817136115660768</v>
+        <v>0.2781714215911059</v>
       </c>
       <c r="N41">
-        <v>0.2116352146334996</v>
+        <v>0.2116353018971933</v>
       </c>
       <c r="O41">
-        <v>0.17753711995880581</v>
+        <v>0.177537227742737</v>
       </c>
       <c r="P41">
-        <v>0.15548049564668301</v>
+        <v>0.1554806358579406</v>
       </c>
       <c r="Q41">
-        <v>0.15293671561042391</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>57</v>
+        <v>0.1529368690236952</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C42" s="2">
-        <v>0.38612238208107391</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C42">
+        <v>0.3861223745781748</v>
       </c>
       <c r="D42">
-        <v>0.49289017139905089</v>
+        <v>0.4928901723252465</v>
       </c>
       <c r="E42">
-        <v>0.46537420627912818</v>
+        <v>0.4653742091673932</v>
       </c>
       <c r="F42">
-        <v>0.41513357268656692</v>
+        <v>0.4151335810810629</v>
       </c>
       <c r="G42">
-        <v>0.45071596944935682</v>
+        <v>0.4507159839166924</v>
       </c>
       <c r="H42">
-        <v>0.43467604920589231</v>
+        <v>0.4346760580911515</v>
       </c>
       <c r="I42">
-        <v>0.43466679951658133</v>
+        <v>0.4346668087606783</v>
       </c>
       <c r="J42">
-        <v>0.4197313035595362</v>
+        <v>0.4197313180915321</v>
       </c>
       <c r="K42">
-        <v>0.32496611975219608</v>
+        <v>0.3249661487618566</v>
       </c>
       <c r="L42">
-        <v>0.24836072410776849</v>
+        <v>0.2483607604480312</v>
       </c>
       <c r="M42">
-        <v>0.1976359338205764</v>
+        <v>0.197636017868631</v>
       </c>
       <c r="N42">
-        <v>0.20546299714259419</v>
+        <v>0.2054631207571058</v>
       </c>
       <c r="O42">
-        <v>0.19402439985299411</v>
+        <v>0.1940245173869739</v>
       </c>
       <c r="P42">
-        <v>0.20262330080731419</v>
+        <v>0.2026234375251185</v>
       </c>
       <c r="Q42">
-        <v>0.22453326455558731</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>58</v>
+        <v>0.2245334594829903</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>-1.8778932657874E-2</v>
-      </c>
-      <c r="C43" s="2">
-        <v>0.50718352427640723</v>
+        <v>-0.018778932657874</v>
+      </c>
+      <c r="C43">
+        <v>0.5071835243123114</v>
       </c>
       <c r="D43">
-        <v>0.49259948980498031</v>
+        <v>0.4925994895329941</v>
       </c>
       <c r="E43">
-        <v>0.49697733490051399</v>
+        <v>0.4969773359924192</v>
       </c>
       <c r="F43">
-        <v>0.45549692251313262</v>
+        <v>0.4554969226009838</v>
       </c>
       <c r="G43">
-        <v>0.43288095899871343</v>
+        <v>0.4328809610159076</v>
       </c>
       <c r="H43">
-        <v>0.41764258215119332</v>
+        <v>0.4176425848082056</v>
       </c>
       <c r="I43">
-        <v>0.43732924364825648</v>
+        <v>0.4373292476206552</v>
       </c>
       <c r="J43">
-        <v>0.44124722987408632</v>
+        <v>0.4412472377772101</v>
       </c>
       <c r="K43">
-        <v>0.43402843630929738</v>
+        <v>0.4340284496415484</v>
       </c>
       <c r="L43">
-        <v>0.37423876561699387</v>
+        <v>0.3742387830681377</v>
       </c>
       <c r="M43">
-        <v>0.3394582960296656</v>
+        <v>0.3394583150170661</v>
       </c>
       <c r="N43">
-        <v>0.31117420027070808</v>
+        <v>0.3111742251960219</v>
       </c>
       <c r="O43">
-        <v>0.3017044073916974</v>
+        <v>0.3017044504926601</v>
       </c>
       <c r="P43">
-        <v>0.29795475033017937</v>
+        <v>0.2979548224681601</v>
       </c>
       <c r="Q43">
-        <v>0.27709203492215201</v>
+        <v>0.2770921610725019</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:Q43">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>